--- a/ocaml实验数据统计(1).xlsx
+++ b/ocaml实验数据统计(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24225" windowHeight="12420" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24225" windowHeight="12420" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="160">
   <si>
     <t>AggregatePassThrough</t>
   </si>
@@ -540,6 +540,18 @@
   </si>
   <si>
     <t>circuits</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BundleVec</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GCD</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mytestinst1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4189,7 +4201,7 @@
     </row>
     <row r="17" spans="1:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="B17" s="3">
         <v>30</v>
@@ -5180,8 +5192,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A4" s="7" t="s">
-        <v>53</v>
+      <c r="A4" s="35" t="s">
+        <v>159</v>
       </c>
       <c r="B4" s="7">
         <v>50</v>
@@ -5252,6 +5264,7 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5517,7 +5530,7 @@
     </row>
     <row r="13" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="B13" s="7">
         <v>405</v>
